--- a/xls/square_12_tri3_10.xlsx
+++ b/xls/square_12_tri3_10.xlsx
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -482,13 +482,13 @@
         <v>600</v>
       </c>
       <c r="I10">
-        <v>2.6307240424956184</v>
+        <v>2.6307237271869286</v>
       </c>
       <c r="J10">
-        <v>-0.45306127755620534</v>
+        <v>-0.4530616053903756</v>
       </c>
       <c r="K10">
-        <v>0.5688589643414742</v>
+        <v>0.5688586845976804</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -517,13 +517,13 @@
         <v>726</v>
       </c>
       <c r="I11">
-        <v>-2.0073842309081678</v>
+        <v>-2.007384364798353</v>
       </c>
       <c r="J11">
-        <v>-1.8095686981236638</v>
+        <v>-1.8095687045457918</v>
       </c>
       <c r="K11">
-        <v>-1.2497852134054146</v>
+        <v>-1.2497852349942713</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -552,13 +552,13 @@
         <v>864</v>
       </c>
       <c r="I12">
-        <v>-2.000714255733095</v>
+        <v>-2.0007143539935885</v>
       </c>
       <c r="J12">
-        <v>-1.8145765709023036</v>
+        <v>-1.8145764828751927</v>
       </c>
       <c r="K12">
-        <v>-1.3188450717086573</v>
+        <v>-1.3188448378460877</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1014</v>
       </c>
       <c r="I13">
-        <v>-1.9752913044907807</v>
+        <v>-1.9752913765199203</v>
       </c>
       <c r="J13">
-        <v>-1.6075629999562548</v>
+        <v>-1.6075630346059628</v>
       </c>
       <c r="K13">
-        <v>1.0875578523259433</v>
+        <v>1.0875522436997718</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>-1.5699246087514083</v>
+        <v>-1.569924532979893</v>
       </c>
       <c r="J14">
-        <v>-1.1513684266350326</v>
+        <v>-1.1513684013675847</v>
       </c>
       <c r="K14">
-        <v>3.031711880954366</v>
+        <v>3.0317118853689817</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-0.22381042705327467</v>
+        <v>-0.22381042615661284</v>
       </c>
       <c r="J15">
-        <v>-0.1852578813005967</v>
+        <v>-0.185257880863682</v>
       </c>
       <c r="K15">
-        <v>3.885701805502609</v>
+        <v>3.8857018049205565</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -692,13 +692,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-0.005470542919183952</v>
+        <v>-0.005470542919634289</v>
       </c>
       <c r="J16">
-        <v>-0.005308005136767033</v>
+        <v>-0.005308005137449826</v>
       </c>
       <c r="K16">
-        <v>3.3044607989766654</v>
+        <v>3.304460798843568</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -727,13 +727,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-0.0001384277533004613</v>
+        <v>-0.00013842775329443236</v>
       </c>
       <c r="J17">
-        <v>-8.671127619250007e-5</v>
+        <v>-8.67112761899441e-5</v>
       </c>
       <c r="K17">
-        <v>2.176199364366147</v>
+        <v>2.176199364414369</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -762,13 +762,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-8.127376737605885e-5</v>
+        <v>-8.127376737673401e-5</v>
       </c>
       <c r="J18">
-        <v>-6.418945907333359e-5</v>
+        <v>-6.418945907405694e-5</v>
       </c>
       <c r="K18">
-        <v>2.269824516404951</v>
+        <v>2.2698245163528528</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -797,13 +797,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>7.715822545160381e-6</v>
+        <v>7.71582254506395e-6</v>
       </c>
       <c r="J19">
-        <v>2.176438283939333e-6</v>
+        <v>2.176438283650036e-6</v>
       </c>
       <c r="K19">
-        <v>1.769032860340561</v>
+        <v>1.769032860160814</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -832,13 +832,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-1.4384693193950515e-5</v>
+        <v>-1.4384693193612989e-5</v>
       </c>
       <c r="J20">
-        <v>-9.144339711737996e-6</v>
+        <v>-9.144339711352257e-6</v>
       </c>
       <c r="K20">
-        <v>1.6963915321181224</v>
+        <v>1.6963915321075345</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -870,10 +870,10 @@
         <v>2.6927488575603537e-9</v>
       </c>
       <c r="J21">
-        <v>-1.8827690125603678e-7</v>
+        <v>-1.8827690135246957e-7</v>
       </c>
       <c r="K21">
-        <v>1.2483565627152977</v>
+        <v>1.2483565627702171</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -902,13 +902,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-2.862026943554723e-7</v>
+        <v>-2.862026943072559e-7</v>
       </c>
       <c r="J22">
-        <v>-2.705835563121777e-7</v>
+        <v>-2.705835562639613e-7</v>
       </c>
       <c r="K22">
-        <v>1.1510988458023055</v>
+        <v>1.151098846048944</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -937,13 +937,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-6.728836752229046e-7</v>
+        <v>-6.728836751746882e-7</v>
       </c>
       <c r="J23">
-        <v>-5.006448186317465e-7</v>
+        <v>-5.006448187281793e-7</v>
       </c>
       <c r="K23">
-        <v>1.1964163797554457</v>
+        <v>1.1964163799845375</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -972,13 +972,293 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-1.7647877969365028e-7</v>
+        <v>-1.7647877954900112e-7</v>
       </c>
       <c r="J24">
-        <v>-1.581394389659996e-7</v>
+        <v>-1.5813943915886517e-7</v>
       </c>
       <c r="K24">
-        <v>1.0221462922758722</v>
+        <v>1.0221462920718287</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25">
+        <v>121</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25">
+        <v>169</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>676</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25">
+        <v>3750</v>
+      </c>
+      <c r="I25">
+        <v>-9.298855402326249e-8</v>
+      </c>
+      <c r="J25">
+        <v>-1.3224134588658217e-7</v>
+      </c>
+      <c r="K25">
+        <v>1.0718673404535208</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>121</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26">
+        <v>169</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26">
+        <v>729</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26">
+        <v>4056</v>
+      </c>
+      <c r="I26">
+        <v>-3.465469303648871e-7</v>
+      </c>
+      <c r="J26">
+        <v>-3.42652857631549e-7</v>
+      </c>
+      <c r="K26">
+        <v>1.213080861978504</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>121</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27">
+        <v>169</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>784</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27">
+        <v>4374</v>
+      </c>
+      <c r="I27">
+        <v>-2.0629523849990857e-7</v>
+      </c>
+      <c r="J27">
+        <v>-1.705608728119447e-7</v>
+      </c>
+      <c r="K27">
+        <v>1.0121930874105478</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>121</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>169</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28">
+        <v>841</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28">
+        <v>4704</v>
+      </c>
+      <c r="I28">
+        <v>-1.477671851101954e-7</v>
+      </c>
+      <c r="J28">
+        <v>-1.2800683767734496e-7</v>
+      </c>
+      <c r="K28">
+        <v>0.9659131523858564</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29">
+        <v>121</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>169</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29">
+        <v>900</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29">
+        <v>5046</v>
+      </c>
+      <c r="I29">
+        <v>-1.3295037351415666e-7</v>
+      </c>
+      <c r="J29">
+        <v>-1.2446683907254077e-7</v>
+      </c>
+      <c r="K29">
+        <v>0.9835468902060617</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>121</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>169</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30">
+        <v>961</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30">
+        <v>5400</v>
+      </c>
+      <c r="I30">
+        <v>-2.0833244884483574e-7</v>
+      </c>
+      <c r="J30">
+        <v>-1.9514658834690664e-7</v>
+      </c>
+      <c r="K30">
+        <v>1.0788317877578941</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <v>121</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>169</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <v>1024</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31">
+        <v>5766</v>
+      </c>
+      <c r="I31">
+        <v>-1.3249228113488974e-7</v>
+      </c>
+      <c r="J31">
+        <v>-1.203914318038779e-7</v>
+      </c>
+      <c r="K31">
+        <v>0.9684231266916743</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>121</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>169</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32">
+        <v>1089</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32">
+        <v>6144</v>
+      </c>
+      <c r="I32">
+        <v>-1.3898083197822243e-7</v>
+      </c>
+      <c r="J32">
+        <v>-1.2067746288533975e-7</v>
+      </c>
+      <c r="K32">
+        <v>0.9541150715430242</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_10.xlsx
+++ b/xls/square_12_tri3_10.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>121</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>169</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>384</v>
+      </c>
+      <c r="I8">
+        <v>19.25156784282413</v>
+      </c>
+      <c r="J8">
+        <v>6.800480151497521</v>
+      </c>
+      <c r="K8">
+        <v>6.8374027610235295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>121</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>169</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>486</v>
+      </c>
+      <c r="I9">
+        <v>4.569114942888472</v>
+      </c>
+      <c r="J9">
+        <v>0.8947478490932792</v>
+      </c>
+      <c r="K9">
+        <v>1.6376834695805846</v>
+      </c>
+    </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>11</v>
